--- a/outputs/EVINV-POC-001/phase2/phase2-requirements-traceability-matrix.xlsx
+++ b/outputs/EVINV-POC-001/phase2/phase2-requirements-traceability-matrix.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 2 | Gate: 2 | Generated: 2026-08-18T03:56:08.733Z</v>
+        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 2 | Gate: 2 | Generated: 2026-08-18T12:56:15.583Z</v>
       </c>
     </row>
     <row r="4">

--- a/outputs/EVINV-POC-001/phase2/phase2-requirements-traceability-matrix.xlsx
+++ b/outputs/EVINV-POC-001/phase2/phase2-requirements-traceability-matrix.xlsx
@@ -406,7 +406,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 2 | Gate: 2 | Generated: 2026-08-18T12:56:15.583Z</v>
+        <v>Project: EVINV-POC-001 | Product: EV-INV-800 | Phase: 2 | Gate: 2 | Generated: 2026-08-18T19:53:23.251Z</v>
       </c>
     </row>
     <row r="4">
